--- a/optiroll-frontend/public/optiroll-import-template.xlsx
+++ b/optiroll-frontend/public/optiroll-import-template.xlsx
@@ -397,20 +397,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="7.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="42.83203125" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
+    <col min="11" max="11" width="9.83203125" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -430,24 +431,27 @@
         <v>Width (")</v>
       </c>
       <c r="F1" t="str">
+        <v>Cut (")</v>
+      </c>
+      <c r="G1" t="str">
         <v>Height (")</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Valence (")</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Qty</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Material</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Color</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Pattern</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Roll Widths (m)</v>
       </c>
     </row>
@@ -468,24 +472,27 @@
         <v>48</v>
       </c>
       <c r="F2">
+        <v>1.5</v>
+      </c>
+      <c r="G2">
         <v>72</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>6</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>1</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>Polyester</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>White</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>Plain</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>all</v>
       </c>
     </row>
@@ -506,24 +513,27 @@
         <v>36</v>
       </c>
       <c r="F3">
+        <v>1.5</v>
+      </c>
+      <c r="G3">
         <v>60</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v/>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>Polyester</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>Beige</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>Plain</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>2.5,2.8</v>
       </c>
     </row>
@@ -544,30 +554,33 @@
         <v>24</v>
       </c>
       <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>48</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>6</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>1</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>Blackout</v>
       </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
         <v>Grey</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>Stripe</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>2.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
 </file>